--- a/linkage/data_processing_elements_linkage-NHS.xlsx
+++ b/linkage/data_processing_elements_linkage-NHS.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/292c22834a0ab190/Documents/ProPASS/Linkage/NHS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\twey working files\ProPASS\NHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{026C1775-36E5-45DE-AAA9-46F3F15F496B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3D16852-3CDD-4E1C-AECB-E57AC3AFAA8A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{163080B8-2EEB-4D2A-A036-1F3F79D06BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{63444C23-9E00-4348-B1ED-05F831BC47B5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63444C23-9E00-4348-B1ED-05F831BC47B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$S$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$O$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,18 +62,6 @@
     <t>input_format</t>
   </si>
   <si>
-    <t>input_time_period</t>
-  </si>
-  <si>
-    <t>input_time_collection</t>
-  </si>
-  <si>
-    <t>input_source_information</t>
-  </si>
-  <si>
-    <t>input_informant</t>
-  </si>
-  <si>
     <t>input_keywords</t>
   </si>
   <si>
@@ -300,6 +288,18 @@
 is.na(DIAGNOSE_UNDERLIGGENDE_K) ~ NA_integer_; 
 grepl("^I0|^I11|^I13|^I2|^I3|^I4|^I50|^I51|^I6|^G30|^E10|^E11|^E12|^E13|^E14|^J40|^J41|^J42|^J43|^J44|^J45|^J46|^J47|^J09|^J10|^J11|^J12|^J13|^J14|^J15|^J16|^J17|^J18|^N00|^N01|^N02|^N03|^N04|^N05|^N06|^N07|^N17|^N18|^N19|^N25|^N26|^N27|^V01|^V02|^V03|^V04|^V05|^V06|^V07|^V08|^V09|^V1|^V2|^V3|^V4|^V5|^V6|^V7|^V8|^V9|^W|^X0|^X1|^X2|^X3|^X4|^X5|^Y85|^Y86", DIAGNOSE_UNDERLIGGENDE_K) ~ 0L; 
 ELSE ~ 1L)</t>
+  </si>
+  <si>
+    <t>validation_comment</t>
+  </si>
+  <si>
+    <t>comment_question_for_cohort</t>
+  </si>
+  <si>
+    <t>response_from_cohort_step1</t>
+  </si>
+  <si>
+    <t>Validate what missing values are in input dataset.</t>
   </si>
 </sst>
 </file>
@@ -341,14 +341,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="5"/>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -380,24 +380,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -406,14 +397,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -430,10 +431,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -753,32 +750,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A96D0D0-036F-4639-8FBF-4A4CEF797E7C}">
-  <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R15"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" style="5" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="85.42578125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.42578125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="43.5703125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21" style="5" customWidth="1"/>
-    <col min="11" max="11" width="27.5703125" style="5" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="27.85546875" style="7" customWidth="1"/>
-    <col min="14" max="14" width="36.5703125" style="7" customWidth="1"/>
-    <col min="15" max="15" width="24.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.85546875" style="5" customWidth="1"/>
-    <col min="17" max="17" width="18.85546875" style="5" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="5" customWidth="1"/>
-    <col min="19" max="19" width="57.42578125" style="5" customWidth="1"/>
-    <col min="20" max="16384" width="11.5703125" style="5"/>
+    <col min="1" max="1" width="6.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" style="3" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="85.453125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.54296875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="27.81640625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="24.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.81640625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="14.54296875" style="7" customWidth="1"/>
+    <col min="14" max="14" width="57.453125" style="7" customWidth="1"/>
+    <col min="15" max="15" width="48.26953125" style="8" customWidth="1"/>
+    <col min="16" max="16" width="18.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="11.54296875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +785,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -803,605 +799,604 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="P1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="B10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="B11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="B12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="B13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>17</v>
+      <c r="F14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" s="5" t="s">
+    <row r="15" spans="1:18" ht="145" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="S2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="105" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q7" s="5" t="s">
+      <c r="M15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="R8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="R9" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="R10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S10" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="N15" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="O15" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="R11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="75" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="R12" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="90" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="R13" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="105" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="R14" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S14" s="9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="150" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="P15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="R15" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S15" xr:uid="{2A96D0D0-036F-4639-8FBF-4A4CEF797E7C}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>